--- a/artfynd/A 3912-2026 artfynd.xlsx
+++ b/artfynd/A 3912-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126360093</v>
+        <v>126359922</v>
       </c>
       <c r="B2" t="n">
-        <v>105396</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523902</v>
+        <v>524007</v>
       </c>
       <c r="R2" t="n">
-        <v>6446442</v>
+        <v>6446077</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126360182</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126359922</v>
+        <v>126361130</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524007</v>
+        <v>523937</v>
       </c>
       <c r="R4" t="n">
-        <v>6446077</v>
+        <v>6446473</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126359970</v>
       </c>
       <c r="B5" t="n">
-        <v>105396</v>
+        <v>106244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126361130</v>
+        <v>126360093</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523937</v>
+        <v>523902</v>
       </c>
       <c r="R6" t="n">
-        <v>6446473</v>
+        <v>6446442</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 3912-2026 artfynd.xlsx
+++ b/artfynd/A 3912-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359922</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360182</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126361130</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126359970</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126360093</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>